--- a/testcase/test_test.xlsx
+++ b/testcase/test_test.xlsx
@@ -1,179 +1,257 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21600" windowHeight="9555" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+  <si>
+    <t>case_id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>headers</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>result</t>
+  </si>
+  <si>
+    <t>extract</t>
+  </si>
+  <si>
+    <t>validata</t>
+  </si>
+  <si>
+    <t>测试结束后清理数据库当天的请假记录</t>
+  </si>
+  <si>
+    <t>db_update</t>
+  </si>
+  <si>
+    <t>update gsr_employee_leave_info set del_flag = '2'  where create_by_code = 445;</t>
+  </si>
+  <si>
+    <t>测试结束后查询数据库是否清理完成</t>
+  </si>
+  <si>
+    <t>db_select</t>
+  </si>
+  <si>
+    <t>select * from gsr_employee_leave_info where create_by_code = 445 AND del_flag ='0';</t>
+  </si>
+  <si>
+    <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,162 +551,170 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -682,74 +768,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1001,143 +1024,118 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="inlineStr">
-        <is>
-          <t>case_id</t>
-        </is>
-      </c>
-      <c r="B1" s="0" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C1" s="0" t="inlineStr">
-        <is>
-          <t>headers</t>
-        </is>
-      </c>
-      <c r="D1" s="0" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="E1" s="0" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" s="0" t="inlineStr">
-        <is>
-          <t>data</t>
-        </is>
-      </c>
-      <c r="G1" s="0" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="H1" s="0" t="inlineStr">
-        <is>
-          <t>extract</t>
-        </is>
-      </c>
-      <c r="I1" s="0" t="inlineStr">
-        <is>
-          <t>validata</t>
-        </is>
+    <row r="1" s="1" customFormat="1" ht="50" customHeight="1" spans="1:9">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2" ht="67.5" customHeight="1" s="2">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>管理端代替当前审批人审批</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
-        <is>
-          <t>${headers_admin}</t>
-        </is>
-      </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
-        <is>
-          <t>/api/center/template/trigger/task/1993573306091069441?isProxy=true&amp;approvalResult=2&amp;comment=自动化测试代通过</t>
-        </is>
-      </c>
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>{"$.code": "200",
-"$.msg": "成功"}</t>
-        </is>
-      </c>
+    <row r="2" s="2" customFormat="1" ht="50" customHeight="1" spans="1:9">
+      <c r="A2" s="4">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" s="3" customFormat="1" ht="50" customHeight="1" spans="1:9">
+      <c r="A3" s="4">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="G2:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <sheetData>
-    <row r="2">
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
-        </is>
+    <row r="2" spans="7:7">
+      <c r="G2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="G2:G2"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
   <sheetData>
-    <row r="2">
-      <c r="G2" s="0" t="inlineStr">
-        <is>
-          <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
-        </is>
+    <row r="2" spans="7:7">
+      <c r="G2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/testcase/test_test.xlsx
+++ b/testcase/test_test.xlsx
@@ -1,257 +1,186 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" windowHeight="9555"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21600" windowHeight="9555" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
-  <si>
-    <t>case_id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>headers</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>extract</t>
-  </si>
-  <si>
-    <t>validata</t>
-  </si>
-  <si>
-    <t>测试结束后清理数据库当天的请假记录</t>
-  </si>
-  <si>
-    <t>db_update</t>
-  </si>
-  <si>
-    <t>update gsr_employee_leave_info set del_flag = '2'  where create_by_code = 445;</t>
-  </si>
-  <si>
-    <t>测试结束后查询数据库是否清理完成</t>
-  </si>
-  <si>
-    <t>db_select</t>
-  </si>
-  <si>
-    <t>select * from gsr_employee_leave_info where create_by_code = 445 AND del_flag ='0';</t>
-  </si>
-  <si>
-    <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -551,168 +480,168 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -768,11 +697,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1024,118 +1016,161 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="50" customHeight="1" spans="1:9">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
+    <row r="1" ht="50" customFormat="1" customHeight="1" s="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>headers</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>data</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" ht="50" customHeight="1" spans="1:9">
-      <c r="A2" s="4">
+    <row r="2" ht="50" customFormat="1" customHeight="1" s="2">
+      <c r="A2" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2">
-        <v>2</v>
-      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>测试结束后清理数据库当天的请假记录</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>db_update</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>update gsr_employee_leave_info set del_flag = '2'  where create_by_code = 445;</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="0" t="n"/>
     </row>
-    <row r="3" s="3" customFormat="1" ht="50" customHeight="1" spans="1:9">
-      <c r="A3" s="4">
+    <row r="3" ht="50" customFormat="1" customHeight="1" s="3">
+      <c r="A3" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>测试结束后查询数据库是否清理完成</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>db_select</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>select * from gsr_employee_leave_info where create_by_code = 445 AND del_flag ='0';</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>count:0</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="G2:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="2" spans="7:7">
-      <c r="G2" t="s">
-        <v>15</v>
+    <row r="2">
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="G2:G2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <sheetData>
-    <row r="2" spans="7:7">
-      <c r="G2" t="s">
-        <v>15</v>
+    <row r="2">
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>{"code":200,"msg":"成功","data":null,"rows":null,"total":null}</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/testcase/test_test.xlsx
+++ b/testcase/test_test.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="21600" windowHeight="9555" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -628,7 +628,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -644,6 +644,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1021,8 +1022,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <cols>
+    <col width="60" customWidth="1" style="5" min="7" max="7"/>
+    <col width="28" customWidth="1" style="5" min="10" max="10"/>
+  </cols>
   <sheetData>
     <row r="1" ht="50" customFormat="1" customHeight="1" s="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1057,17 +1062,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>extract</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>validata</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>result</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>extract</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>validata</t>
         </is>
       </c>
     </row>
